--- a/evaluation/scenario_sources/Conversation Scenario-CSimulator.xlsx
+++ b/evaluation/scenario_sources/Conversation Scenario-CSimulator.xlsx
@@ -4218,7 +4218,7 @@
         <v>190</v>
       </c>
       <c r="D114" t="s" s="12">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="E114" s="39"/>
       <c r="F114" t="s" s="5">
